--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Representative.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Representative.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -496,6 +496,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -665,6 +672,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -678,6 +688,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -719,7 +732,14 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -735,6 +755,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -807,6 +830,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -859,6 +885,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1214,7 +1243,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1571,7 +1606,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2895,7 +2930,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2907,15 +2942,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2941,13 +2976,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2973,13 +3008,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2997,7 +3032,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3006,7 +3041,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3018,15 +3053,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3052,13 +3087,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3108,7 +3143,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3134,10 +3169,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3160,16 +3195,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3195,13 +3230,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3219,7 +3254,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3245,14 +3280,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3271,16 +3306,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3330,7 +3365,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3351,19 +3386,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3382,16 +3417,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3441,7 +3476,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3462,15 +3497,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3499,7 +3534,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3540,19 +3575,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3573,15 +3608,15 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3607,16 +3642,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3653,19 +3688,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3686,15 +3721,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3717,19 +3752,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3778,7 +3813,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3787,27 +3822,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>76</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3830,15 +3865,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3887,7 +3924,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3902,21 +3939,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3942,13 +3979,13 @@
         <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3998,7 +4035,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4013,25 +4050,25 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4050,16 +4087,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4109,7 +4146,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4118,31 +4155,31 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4161,15 +4198,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4218,7 +4257,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4227,27 +4266,27 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4270,15 +4309,17 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4327,7 +4368,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4336,10 +4377,10 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
@@ -4348,15 +4389,15 @@
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4379,16 +4420,16 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4414,13 +4455,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4438,7 +4479,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>86</v>
@@ -4453,10 +4494,10 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4464,14 +4505,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4490,16 +4531,16 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4525,31 +4566,31 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4558,27 +4599,27 @@
         <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4601,16 +4642,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4636,13 +4677,13 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4660,7 +4701,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4669,7 +4710,7 @@
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
@@ -4678,18 +4719,18 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4712,23 +4753,23 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>76</v>
@@ -4749,13 +4790,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4773,7 +4814,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4791,7 +4832,7 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -4799,10 +4840,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4825,15 +4866,17 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4858,13 +4901,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4882,7 +4925,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4891,7 +4934,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>98</v>
@@ -4903,19 +4946,19 @@
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4934,15 +4977,17 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -4991,7 +5036,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5000,27 +5045,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5043,16 +5088,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5078,13 +5123,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5102,7 +5147,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5111,7 +5156,7 @@
         <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>98</v>
@@ -5120,18 +5165,18 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5154,16 +5199,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5213,7 +5258,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5222,27 +5267,27 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5265,16 +5310,16 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5324,7 +5369,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5333,27 +5378,27 @@
         <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5376,13 +5421,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5433,7 +5478,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5448,10 +5493,10 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5459,10 +5504,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5485,13 +5530,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5542,7 +5587,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5557,10 +5602,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5568,10 +5613,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5594,15 +5639,17 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5651,7 +5698,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5660,27 +5707,27 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5786,10 +5833,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5897,10 +5944,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5926,13 +5973,13 @@
         <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5982,7 +6029,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5991,7 +6038,7 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>98</v>
@@ -6003,15 +6050,15 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6037,13 +6084,13 @@
         <v>128</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6072,10 +6119,10 @@
         <v>150</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6093,7 +6140,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6114,15 +6161,15 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6145,16 +6192,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6204,7 +6251,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6213,7 +6260,7 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>98</v>
@@ -6225,15 +6272,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6259,13 +6306,13 @@
         <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6315,7 +6362,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6336,15 +6383,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6367,15 +6414,17 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6424,7 +6473,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6433,27 +6482,27 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6559,10 +6608,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6670,10 +6719,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6699,13 +6748,13 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6755,7 +6804,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6764,7 +6813,7 @@
         <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>98</v>
@@ -6776,15 +6825,15 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6810,13 +6859,13 @@
         <v>128</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6845,10 +6894,10 @@
         <v>150</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6866,7 +6915,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6887,15 +6936,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6918,16 +6967,16 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6977,7 +7026,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6986,7 +7035,7 @@
         <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>98</v>
@@ -6998,15 +7047,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7032,13 +7081,13 @@
         <v>100</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7088,7 +7137,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7109,15 +7158,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7140,16 +7189,16 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7175,13 +7224,13 @@
         <v>76</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7199,7 +7248,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7208,27 +7257,27 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7251,15 +7300,17 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7308,7 +7359,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7317,27 +7368,27 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7360,13 +7411,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7417,7 +7468,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7426,7 +7477,7 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7438,15 +7489,15 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7552,10 +7603,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7625,16 +7676,16 @@
         <v>76</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>114</v>
@@ -7663,14 +7714,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7692,16 +7743,16 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7750,7 +7801,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7771,15 +7822,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7805,10 +7856,10 @@
         <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7859,7 +7910,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>86</v>
@@ -7868,7 +7919,7 @@
         <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
@@ -7880,15 +7931,15 @@
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7911,15 +7962,17 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -7968,7 +8021,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7977,19 +8030,19 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>76</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Representative.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-Representative.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="384">
   <si>
     <t>Property</t>
   </si>
@@ -496,13 +496,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -672,9 +665,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -688,9 +678,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -732,14 +719,7 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -755,9 +735,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -830,9 +807,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -885,9 +859,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1243,13 +1214,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1571,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2930,7 +2895,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2942,15 +2907,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2976,13 +2941,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3008,31 +2973,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3041,7 +3006,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3053,15 +3018,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3087,13 +3052,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3143,7 +3108,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3169,10 +3134,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3195,16 +3160,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3230,31 +3195,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3280,14 +3245,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3306,16 +3271,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3365,7 +3330,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3386,19 +3351,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3417,16 +3382,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3476,7 +3441,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3497,15 +3462,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3534,7 +3499,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3575,19 +3540,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3608,15 +3573,15 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3642,16 +3607,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3688,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3721,15 +3686,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3752,19 +3717,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3813,7 +3778,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3822,27 +3787,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3865,17 +3830,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3924,7 +3887,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3939,21 +3902,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3979,13 +3942,13 @@
         <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4035,7 +3998,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4050,25 +4013,25 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4087,16 +4050,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4146,7 +4109,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4155,31 +4118,31 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4198,17 +4161,15 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4257,7 +4218,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4266,27 +4227,27 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4309,17 +4270,15 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4368,7 +4327,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4377,10 +4336,10 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
@@ -4389,15 +4348,15 @@
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4420,16 +4379,16 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4455,13 +4414,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4479,7 +4438,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>86</v>
@@ -4494,10 +4453,10 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4505,14 +4464,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4531,16 +4490,16 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4566,13 +4525,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4590,7 +4549,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4599,27 +4558,27 @@
         <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4642,16 +4601,16 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4677,13 +4636,13 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4701,7 +4660,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4710,7 +4669,7 @@
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
@@ -4719,18 +4678,18 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4753,23 +4712,23 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>76</v>
@@ -4790,13 +4749,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4814,7 +4773,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4832,7 +4791,7 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -4840,10 +4799,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4866,17 +4825,15 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4901,13 +4858,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4925,7 +4882,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4934,7 +4891,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>98</v>
@@ -4946,19 +4903,19 @@
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4977,17 +4934,15 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5036,7 +4991,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5045,27 +5000,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5088,16 +5043,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5123,13 +5078,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5147,7 +5102,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5156,7 +5111,7 @@
         <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>98</v>
@@ -5165,18 +5120,18 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5199,16 +5154,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5258,7 +5213,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5267,27 +5222,27 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5310,16 +5265,16 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5369,7 +5324,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5378,27 +5333,27 @@
         <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5421,13 +5376,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5478,7 +5433,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5493,10 +5448,10 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5504,10 +5459,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5530,13 +5485,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5587,7 +5542,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5602,10 +5557,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5613,10 +5568,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5639,17 +5594,15 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5698,7 +5651,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5707,27 +5660,27 @@
         <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5833,10 +5786,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5944,10 +5897,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5973,13 +5926,13 @@
         <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6029,7 +5982,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6038,7 +5991,7 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>98</v>
@@ -6050,15 +6003,15 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6084,13 +6037,13 @@
         <v>128</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6119,10 +6072,10 @@
         <v>150</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6140,7 +6093,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6161,15 +6114,15 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6192,16 +6145,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6251,7 +6204,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6260,7 +6213,7 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>98</v>
@@ -6272,15 +6225,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6306,13 +6259,13 @@
         <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6362,7 +6315,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6383,15 +6336,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6414,17 +6367,15 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6473,7 +6424,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6482,27 +6433,27 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6608,10 +6559,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6719,10 +6670,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6748,13 +6699,13 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6804,7 +6755,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6813,7 +6764,7 @@
         <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>98</v>
@@ -6825,15 +6776,15 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6859,13 +6810,13 @@
         <v>128</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6894,10 +6845,10 @@
         <v>150</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6915,7 +6866,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6936,15 +6887,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6967,16 +6918,16 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7026,7 +6977,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7035,7 +6986,7 @@
         <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>98</v>
@@ -7047,15 +6998,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7081,13 +7032,13 @@
         <v>100</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7137,7 +7088,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7158,15 +7109,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7189,16 +7140,16 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7224,13 +7175,13 @@
         <v>76</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7248,7 +7199,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7257,27 +7208,27 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7300,17 +7251,15 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7359,7 +7308,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7368,27 +7317,27 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7411,13 +7360,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7468,7 +7417,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7477,7 +7426,7 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7489,15 +7438,15 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7603,10 +7552,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7676,16 +7625,16 @@
         <v>76</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>114</v>
@@ -7714,14 +7663,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7743,16 +7692,16 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7801,7 +7750,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7822,15 +7771,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7856,10 +7805,10 @@
         <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7910,7 +7859,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>86</v>
@@ -7919,7 +7868,7 @@
         <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
@@ -7931,15 +7880,15 @@
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7962,17 +7911,15 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8021,7 +7968,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8030,19 +7977,19 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>394</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
